--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -1,3 +1,20 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sammenlagt" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historikk" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LEV" sheetId="3" state="visible" r:id="rId3"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -390,4 +407,152 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LEV</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LEV</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LEV</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -9,7 +9,15 @@
   <sheets>
     <sheet name="Sammenlagt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historikk" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LEV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AHH" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="EB" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="JH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KAF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LEV" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="RB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TOH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UTG" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ØG" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +446,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KAF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>220</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AHH</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>LEV</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
+      <c r="B6" t="n">
+        <v>200</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UTG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ØG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>160</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>120</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -453,7 +565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -487,17 +599,249 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>UTG</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ØG</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AHH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>220</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KAF</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>LEV</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>260</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>180</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UTG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ØG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -539,6 +883,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AHH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KAF</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>240</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>LEV</t>
         </is>
       </c>
@@ -546,10 +1098,114 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>260</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TOH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>180</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -132,6 +132,145 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Poeng per spiller</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sammenlagt'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sammenlagt'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sammenlagt'!$B$2:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Spiller</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Poeng</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,6 +701,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -255,7 +255,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="7200000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -585,11 +585,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AHH</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -598,11 +598,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>KAF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -611,11 +611,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -624,11 +624,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KAF</t>
+          <t>AHH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -637,11 +637,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ØG</t>
+          <t>UTG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -650,11 +650,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>LEV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -676,11 +676,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UTG</t>
+          <t>ØG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -689,11 +689,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>

--- a/tippelag.xlsx
+++ b/tippelag.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet name="Sammenlagt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historikk" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AHH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="EB" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="JH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="KAF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="LEV" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="RB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TOH" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="UTG" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ØG" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Kuponger" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AHH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="EB" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="JH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KAF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LEV" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="RB" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TOH" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="UTG" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ØG" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,14 +740,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UTG</t>
+          <t>TOH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -791,6 +792,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>UTG</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Navn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Uke</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Poeng</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rette</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>ØG</t>
         </is>
       </c>
@@ -995,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,35 +1059,249 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Uke</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Poeng</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Rette</t>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Sum</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KAF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>AHH</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UTG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LEV</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ØG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1075,14 +1342,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EB</t>
+          <t>AHH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1127,14 +1394,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>EB</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1179,14 +1446,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KAF</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1231,14 +1498,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>KAF</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1283,14 +1550,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LEV</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1335,14 +1602,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TOH</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
